--- a/Result/profitability/1760.xlsx
+++ b/Result/profitability/1760.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM57"/>
+  <dimension ref="A1:AM58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.55</v>
       </c>
       <c r="M2" t="n">
-        <v>0.50875</v>
+        <v>0.52625</v>
       </c>
       <c r="N2" t="n">
-        <v>52.45</v>
+        <v>52.32</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0.44375</v>
+        <v>0.45375</v>
       </c>
       <c r="N3" t="n">
-        <v>52.28125</v>
+        <v>52.2625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3775</v>
+        <v>0.39375</v>
       </c>
       <c r="N4" t="n">
-        <v>52.23875</v>
+        <v>51.76375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.32</v>
       </c>
       <c r="M5" t="n">
-        <v>0.37625</v>
+        <v>0.37875</v>
       </c>
       <c r="N5" t="n">
-        <v>52.335</v>
+        <v>51.9975</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.75</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2275</v>
+        <v>0.175</v>
       </c>
       <c r="N6" t="n">
-        <v>52.47750000000001</v>
+        <v>51.74875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.43</v>
       </c>
       <c r="M7" t="n">
-        <v>0.06375</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>52.57625</v>
+        <v>52.36</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -7667,6 +7667,133 @@
       </c>
       <c r="AM57" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1760</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>512</v>
+      </c>
+      <c r="D58" t="n">
+        <v>253</v>
+      </c>
+      <c r="E58" t="n">
+        <v>259</v>
+      </c>
+      <c r="F58" t="n">
+        <v>50.62</v>
+      </c>
+      <c r="G58" t="n">
+        <v>62</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>12.09%</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>61</v>
+      </c>
+      <c r="K58" t="n">
+        <v>39</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.4975</v>
+      </c>
+      <c r="N58" t="n">
+        <v>52.6825</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
+      </c>
+      <c r="V58" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W58" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="X58" t="n">
+        <v>-0.2333333333333333</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-0.02409870830923466</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0.04545454545454541</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>-2.700000000000003</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>-0.05063765941485376</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK58" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
